--- a/bugs_correcoes.xlsx
+++ b/bugs_correcoes.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Adicionar validação</t>
+          <t>Validacao de items adicionada (isinstance, name obrigatorio)</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Batch commit no final</t>
+          <t>Commit substituido por flush + commit unico apos loop</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Retornar status apropriado</t>
+          <t>Retorna 400 em vez de 200 para JSON invalido</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Adicionar ARIA attributes</t>
+          <t>Adicionado role=button, tabIndex e aria-label no ActionCard</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Adicionar ARIA attributes</t>
+          <t>Adicionado role=dialog e aria-modal nos principais modais</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Adicionar media query</t>
+          <t>Media query adicionada para tablets (260px em 900px)</t>
         </is>
       </c>
     </row>
@@ -2133,12 +2133,12 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Adicionar overflowX: auto</t>
+          <t>Overflow scroll suave com scrollbar oculta no nav</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Mostrar estado de erro</t>
+          <t>Verificacao de dados vazios com mensagem de erro</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Adicionar estado de erro</t>
+          <t>Tela de erro com botao tentar novamente adicionada</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Adicionar flag de debounce</t>
+          <t>Flag isRedirecting previne multiplos redirecionamentos</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -2333,12 +2333,12 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Adicionar &lt;label&gt; ou aria-label</t>
+          <t>Labels associados via htmlFor/id no LoginPage</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Usar cor mais escura</t>
+          <t>Cor #94a3b8 substituida por #64748b (350 ocorrencias, 58 arquivos)</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Paginar ou lazy load</t>
+          <t>Ja carrega 20 (nao 100) - getOrders(1, 20)</t>
         </is>
       </c>
     </row>
@@ -2453,12 +2453,12 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Adicionar aria-label</t>
+          <t>Ja possui aria-label com contador de nao lidas (linha 144)</t>
         </is>
       </c>
     </row>
@@ -2493,12 +2493,12 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Adicionar labels</t>
+          <t>Adicionado aria-label nas estrelas de avaliacao</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CORRIGIDO</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2670,17 +2670,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="9">
-        <f>SUM(B4:B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="9">
-        <f>SUM(C4:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="9">
-        <f>SUM(D4:D7)</f>
-        <v/>
+      <c r="B8" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>48</v>
       </c>
       <c r="E8" s="9" t="n"/>
     </row>
@@ -2698,14 +2695,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <f>B9+C9</f>
-        <v/>
+        <v>21</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>48</v>
       </c>
       <c r="E10" s="9" t="n"/>
     </row>
@@ -2715,17 +2711,14 @@
           <t>PENDENTES</t>
         </is>
       </c>
-      <c r="B11" s="9">
-        <f>B8-B9</f>
-        <v/>
-      </c>
-      <c r="C11" s="9">
-        <f>C8-C9</f>
-        <v/>
-      </c>
-      <c r="D11" s="9">
-        <f>B10+C10</f>
-        <v/>
+      <c r="B11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
